--- a/JK_auto/测试用例.xlsx
+++ b/JK_auto/测试用例.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\files\py_project\PythonProject\PythonProject\autoTest\JK_auto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\files\git_file\JK_auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E95193-07AE-4562-99E6-0CFDB53ECA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52902B5E-2958-499B-9D70-7982874A45DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>描述</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -329,10 +329,6 @@
   </si>
   <si>
     <t>http://shop-xo.hctestedu.com/index.php?s=api/goods/favor&amp;token=${token}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>count</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -775,9 +771,6 @@
       <c r="G3">
         <v>200</v>
       </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
